--- a/Alwin-RMTest-T107357.xlsx
+++ b/Alwin-RMTest-T107357.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -32,24 +32,6 @@
   </si>
   <si>
     <t>Linearität</t>
-  </si>
-  <si>
-    <t>Mittelposition</t>
-  </si>
-  <si>
-    <t>Start aktiver Bereich CW (Drehrichtung-)</t>
-  </si>
-  <si>
-    <t>50° CW (25% aktiver Bereich)(Drehrichtung-)</t>
-  </si>
-  <si>
-    <t>75° CW (50% aktiver Bereich)(Drehrichtung-)</t>
-  </si>
-  <si>
-    <t>100° CW (75% aktiver Bereich)(Drehrichtung-)</t>
-  </si>
-  <si>
-    <t>Ende aktiver Bereich CW (Drehrichtung-)(11) 10V</t>
   </si>
   <si>
     <t>Mechanisches Ende CW (Drehrichtung-)</t>
@@ -77,10 +59,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="0,0°"/>
-    <numFmt numFmtId="165" formatCode="0,000"/>
-    <numFmt numFmtId="166" formatCode="0,00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0°"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -134,11 +117,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -436,33 +428,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="20.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -476,13 +469,13 @@
       <c r="C2" s="2">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>3</v>
       </c>
       <c r="E2" s="1">
-        <v>-0</v>
-      </c>
-      <c r="F2" s="3">
+        <v>-0.1</v>
+      </c>
+      <c r="F2" s="4">
         <v>-0.2</v>
       </c>
     </row>
@@ -496,13 +489,13 @@
       <c r="C3" s="2">
         <v>5</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>4</v>
       </c>
       <c r="E3" s="1">
-        <v>24.4</v>
-      </c>
-      <c r="F3" s="3">
+        <v>24.3</v>
+      </c>
+      <c r="F3" s="4">
         <v>-0.1</v>
       </c>
     </row>
@@ -516,13 +509,13 @@
       <c r="C4" s="2">
         <v>6.25</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>4</v>
       </c>
       <c r="E4" s="1">
-        <v>49.4</v>
-      </c>
-      <c r="F4" s="3">
+        <v>49.3</v>
+      </c>
+      <c r="F4" s="4">
         <v>-0.22</v>
       </c>
     </row>
@@ -536,13 +529,13 @@
       <c r="C5" s="2">
         <v>7.5</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>5</v>
       </c>
       <c r="E5" s="1">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="F5" s="3">
+        <v>74.3</v>
+      </c>
+      <c r="F5" s="4">
         <v>-0.25</v>
       </c>
     </row>
@@ -556,13 +549,13 @@
       <c r="C6" s="2">
         <v>8.75</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>6</v>
       </c>
       <c r="E6" s="1">
         <v>99.3</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="4">
         <v>-0.27</v>
       </c>
     </row>
@@ -576,13 +569,13 @@
       <c r="C7" s="2">
         <v>10</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>6</v>
       </c>
       <c r="E7" s="1">
-        <v>124.4</v>
-      </c>
-      <c r="F7" s="3">
+        <v>124.3</v>
+      </c>
+      <c r="F7" s="4">
         <v>-0.4</v>
       </c>
     </row>
@@ -596,134 +589,14 @@
       <c r="C8" s="2">
         <v>10</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>7</v>
       </c>
       <c r="E8" s="1">
         <v>165.5</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="4">
         <v>-0.3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="1">
-        <v>-25</v>
-      </c>
-      <c r="C9" s="2">
-        <v>5</v>
-      </c>
-      <c r="D9" s="2">
-        <v>3</v>
-      </c>
-      <c r="E9" s="1">
-        <v>-25.6</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="1">
-        <v>-50</v>
-      </c>
-      <c r="C10" s="2">
-        <v>3.75</v>
-      </c>
-      <c r="D10" s="2">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1">
-        <v>-50.7</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="1">
-        <v>-75</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2.5</v>
-      </c>
-      <c r="D11" s="2">
-        <v>2</v>
-      </c>
-      <c r="E11" s="1">
-        <v>-75.59999999999999</v>
-      </c>
-      <c r="F11" s="3">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1">
-        <v>-100</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1.25</v>
-      </c>
-      <c r="D12" s="2">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>-100.6</v>
-      </c>
-      <c r="F12" s="3">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="1">
-        <v>-125</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1">
-        <v>-125.7</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1">
-        <v>-165.6</v>
-      </c>
-      <c r="C14" s="2">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2">
-        <v>0</v>
-      </c>
-      <c r="E14" s="1">
-        <v>-165.6</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Alwin-RMTest-T107357.xlsx
+++ b/Alwin-RMTest-T107357.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -32,6 +32,24 @@
   </si>
   <si>
     <t>Linearität</t>
+  </si>
+  <si>
+    <t>Mittelposition</t>
+  </si>
+  <si>
+    <t>Start aktiver Bereich CW (Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>50° CW (25% aktiver Bereich)(Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>75° CW (50% aktiver Bereich)(Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>100° CW (75% aktiver Bereich)(Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>Ende aktiver Bereich CW (Drehrichtung-)(11) 10V</t>
   </si>
   <si>
     <t>Mechanisches Ende CW (Drehrichtung-)</t>
@@ -428,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.7109375" customWidth="1"/>
@@ -470,13 +488,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1">
-        <v>-0.1</v>
+        <v>-0</v>
       </c>
       <c r="F2" s="4">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -490,13 +508,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E3" s="1">
-        <v>24.3</v>
+        <v>24.9</v>
       </c>
       <c r="F3" s="4">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -510,13 +528,13 @@
         <v>6.25</v>
       </c>
       <c r="D4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4" s="1">
-        <v>49.3</v>
+        <v>50</v>
       </c>
       <c r="F4" s="4">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -530,13 +548,13 @@
         <v>7.5</v>
       </c>
       <c r="D5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E5" s="1">
-        <v>74.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F5" s="4">
-        <v>-0.25</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -550,13 +568,13 @@
         <v>8.75</v>
       </c>
       <c r="D6" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1">
-        <v>99.3</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F6" s="4">
-        <v>-0.27</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -570,13 +588,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" s="1">
-        <v>124.3</v>
+        <v>125</v>
       </c>
       <c r="F7" s="4">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -590,13 +608,133 @@
         <v>10</v>
       </c>
       <c r="D8" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="1">
-        <v>165.5</v>
+        <v>165.6</v>
       </c>
       <c r="F8" s="4">
-        <v>-0.3</v>
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-25</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-50</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-50</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-75</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-74.90000000000001</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="F12" s="4">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-125</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-125</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-165.6</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>-1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-165.6</v>
+      </c>
+      <c r="F14" s="4">
+        <v>-0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Alwin-RMTest-T107357.xlsx
+++ b/Alwin-RMTest-T107357.xlsx
@@ -488,13 +488,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E2" s="1">
         <v>-0</v>
       </c>
       <c r="F2" s="4">
-        <v>-0.3</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -508,13 +508,13 @@
         <v>5</v>
       </c>
       <c r="D3" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E3" s="1">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -528,13 +528,13 @@
         <v>6.25</v>
       </c>
       <c r="D4" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E4" s="1">
-        <v>50</v>
+        <v>49.9</v>
       </c>
       <c r="F4" s="4">
-        <v>-0.32</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -548,13 +548,13 @@
         <v>7.5</v>
       </c>
       <c r="D5" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E5" s="1">
         <v>74.90000000000001</v>
       </c>
       <c r="F5" s="4">
-        <v>-0.45</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -568,13 +568,13 @@
         <v>8.75</v>
       </c>
       <c r="D6" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1">
         <v>99.90000000000001</v>
       </c>
       <c r="F6" s="4">
-        <v>-0.47</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -588,13 +588,13 @@
         <v>10</v>
       </c>
       <c r="D7" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1">
         <v>125</v>
       </c>
       <c r="F7" s="4">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -608,13 +608,13 @@
         <v>10</v>
       </c>
       <c r="D8" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1">
-        <v>165.6</v>
+        <v>165.5</v>
       </c>
       <c r="F8" s="4">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -628,13 +628,13 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" s="1">
         <v>-25</v>
       </c>
       <c r="F9" s="4">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -648,13 +648,13 @@
         <v>3.75</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1">
         <v>-50</v>
       </c>
       <c r="F10" s="4">
-        <v>-0.28</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -668,13 +668,13 @@
         <v>2.5</v>
       </c>
       <c r="D11" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <v>-74.90000000000001</v>
       </c>
       <c r="F11" s="4">
-        <v>-0.25</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -688,13 +688,13 @@
         <v>1.25</v>
       </c>
       <c r="D12" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
         <v>-99.90000000000001</v>
       </c>
       <c r="F12" s="4">
-        <v>-0.13</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="1">
         <v>-125</v>
       </c>
       <c r="F13" s="4">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -728,13 +728,13 @@
         <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="1">
         <v>-165.6</v>
       </c>
       <c r="F14" s="4">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Alwin-RMTest-T107357.xlsx
+++ b/Alwin-RMTest-T107357.xlsx
@@ -13,6 +13,68 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Soll-Winkel [°]</t>
+  </si>
+  <si>
+    <t>Soll-Spannung [V]</t>
+  </si>
+  <si>
+    <t>Ist-Spannung [V]</t>
+  </si>
+  <si>
+    <t>Ist-Winkel [°]</t>
+  </si>
+  <si>
+    <t>Linearität</t>
+  </si>
+  <si>
+    <t>Mittelposition</t>
+  </si>
+  <si>
+    <t>Start aktiver Bereich CW (Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>50° CW (25% aktiver Bereich)(Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>75° CW (50% aktiver Bereich)(Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>100° CW (75% aktiver Bereich)(Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>Ende aktiver Bereich CW (Drehrichtung-)(11) 10V</t>
+  </si>
+  <si>
+    <t>Mechanisches Ende CW (Drehrichtung-)</t>
+  </si>
+  <si>
+    <t>Start aktiver Bereich CCW (Drehrichtung+)</t>
+  </si>
+  <si>
+    <t>50° CCW (25% aktiver Bereich)(Drehrichtung+)</t>
+  </si>
+  <si>
+    <t>75° CCW (50% aktiver Bereich)(Drehrichtung+)</t>
+  </si>
+  <si>
+    <t>100° CCW (75% aktiver Bereich)(Drehrichtung+)</t>
+  </si>
+  <si>
+    <t>Ende aktiver Bereich CCW (Drehrichtung+)(13) 0V</t>
+  </si>
+  <si>
+    <t>Mechanisches Ende CCW (Drehrichtung+)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
@@ -21,8 +83,16 @@
     <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -38,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,11 +116,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -63,6 +148,9 @@
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -358,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B1:F1"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="44.7109375" customWidth="1"/>
@@ -368,7 +456,288 @@
     <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="20.7109375" style="4" customWidth="1"/>
   </cols>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3">
+        <v>5.07</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3">
+        <v>5.07</v>
+      </c>
+      <c r="E3" s="1">
+        <v>25.1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1">
+        <v>50</v>
+      </c>
+      <c r="C4" s="2">
+        <v>6.25</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.27</v>
+      </c>
+      <c r="E4" s="1">
+        <v>50</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="1">
+        <v>75</v>
+      </c>
+      <c r="C5" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7.51</v>
+      </c>
+      <c r="E5" s="1">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2">
+        <v>8.75</v>
+      </c>
+      <c r="D6" s="3">
+        <v>8.76</v>
+      </c>
+      <c r="E6" s="1">
+        <v>100.1</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1">
+        <v>125</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10</v>
+      </c>
+      <c r="D7" s="3">
+        <v>10</v>
+      </c>
+      <c r="E7" s="1">
+        <v>125</v>
+      </c>
+      <c r="F7" s="4">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1">
+        <v>166</v>
+      </c>
+      <c r="C8" s="2">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1">
+        <v>166</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="1">
+        <v>-25</v>
+      </c>
+      <c r="C9" s="2">
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>4.88</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-25</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="1">
+        <v>-50</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3.75</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3.66</v>
+      </c>
+      <c r="E10" s="1">
+        <v>-50</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="1">
+        <v>-75</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="D11" s="3">
+        <v>2.44</v>
+      </c>
+      <c r="E11" s="1">
+        <v>-74.90000000000001</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1">
+        <v>-100</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1.21</v>
+      </c>
+      <c r="E12" s="1">
+        <v>-99.8</v>
+      </c>
+      <c r="F12" s="4">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="1">
+        <v>-125</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>-125.1</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-166</v>
+      </c>
+      <c r="C14" s="2">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="1">
+        <v>-166</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Alwin-RMTest-T107357.xlsx
+++ b/Alwin-RMTest-T107357.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Messung"/>
+    <sheet name="Messung" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t xml:space="preserve"> </t>
   </si>
@@ -71,18 +71,31 @@
   </si>
   <si>
     <t>Mechanisches Ende CCW (Drehrichtung+)</t>
+  </si>
+  <si>
+    <t>Totzone</t>
+  </si>
+  <si>
+    <t>Winkel Aktiver Bereich CW (Drehrichtung-)(11)</t>
+  </si>
+  <si>
+    <t>Winkel Aktiver Bereich CCW (Drehrichtung+)(13)</t>
+  </si>
+  <si>
+    <t>Aktive Bereiche Gesamt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00%"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0°"/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -93,15 +106,10 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -112,7 +120,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,88 +130,46 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf xfId="0" numFmtId="166" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -212,10 +178,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -253,71 +219,69 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -341,53 +305,54 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="51000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="94000"/>
+                <a:shade val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="9500"/>
+              <a:shade val="95000"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -397,7 +362,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -406,7 +371,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -415,7 +380,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -423,10 +388,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -455,7 +420,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="20000"/>
+                <a:shade val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -468,12 +433,13 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
+                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -491,299 +457,328 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" style="11" width="44.71928571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="12" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="13" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="12" width="20.719285714285714" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="15" width="20.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="44.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="6" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="1">
         <v>0</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="2">
         <v>5</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="3">
         <v>5.068</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="1">
         <v>-0.1</v>
       </c>
-      <c r="F2" s="10">
-        <v>0.006787</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="4">
+        <v>0.006783</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="1">
         <v>25</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="2">
         <v>5</v>
       </c>
-      <c r="D3" s="9">
-        <v>5.076</v>
-      </c>
-      <c r="E3" s="7">
-        <v>25</v>
-      </c>
-      <c r="F3" s="10">
-        <v>0.007589</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="6" t="s">
+      <c r="D3" s="3">
+        <v>5.068</v>
+      </c>
+      <c r="E3" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.006783</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="1">
         <v>50</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="2">
         <v>6.25</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="3">
         <v>6.302</v>
       </c>
-      <c r="E4" s="7">
-        <v>49.9</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0.005166</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="6" t="s">
+      <c r="E4" s="1">
+        <v>49.8</v>
+      </c>
+      <c r="F4" s="4">
+        <v>0.005171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="1">
         <v>75</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="2">
         <v>7.5</v>
       </c>
-      <c r="D5" s="9">
-        <v>7.547</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="D5" s="3">
+        <v>7.555</v>
+      </c>
+      <c r="E5" s="1">
         <v>75</v>
       </c>
-      <c r="F5" s="10">
-        <v>0.004731</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="6" t="s">
+      <c r="F5" s="4">
+        <v>0.005486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="1">
         <v>100</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="2">
         <v>8.75</v>
       </c>
-      <c r="D6" s="9">
-        <v>8.804</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="D6" s="3">
+        <v>8.805</v>
+      </c>
+      <c r="E6" s="1">
         <v>99.8</v>
       </c>
-      <c r="F6" s="10">
-        <v>0.005419</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="6" t="s">
+      <c r="F6" s="4">
+        <v>0.005508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="1">
         <v>125</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="2">
         <v>10</v>
       </c>
-      <c r="D7" s="9">
-        <v>9.998</v>
-      </c>
-      <c r="E7" s="7">
-        <v>124.9</v>
-      </c>
-      <c r="F7" s="10">
-        <v>-0.000199</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="6" t="s">
+      <c r="D7" s="3">
+        <v>9.997999999999999</v>
+      </c>
+      <c r="E7" s="1">
+        <v>124</v>
+      </c>
+      <c r="F7" s="4">
+        <v>-0.000241</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="7">
-        <v>165.5</v>
-      </c>
-      <c r="C8" s="8">
+      <c r="B8" s="1">
+        <v>165.7</v>
+      </c>
+      <c r="C8" s="2">
         <v>10</v>
       </c>
-      <c r="D8" s="9">
-        <v>9.998</v>
-      </c>
-      <c r="E8" s="7">
-        <v>165.5</v>
-      </c>
-      <c r="F8" s="10">
-        <v>-0.000202</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="6" t="s">
+      <c r="D8" s="3">
+        <v>9.997999999999999</v>
+      </c>
+      <c r="E8" s="1">
+        <v>165.7</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-0.000184</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="1">
         <v>-25</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="2">
         <v>5</v>
       </c>
-      <c r="D9" s="9">
-        <v>4.889</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-25.1</v>
-      </c>
-      <c r="F9" s="10">
-        <v>-0.011079</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="6" t="s">
+      <c r="D9" s="3">
+        <v>5.065</v>
+      </c>
+      <c r="E9" s="1">
+        <v>-18.5</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.006486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="1">
         <v>-50</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="2">
         <v>3.75</v>
       </c>
-      <c r="D10" s="9">
-        <v>3.674</v>
-      </c>
-      <c r="E10" s="7">
+      <c r="D10" s="3">
+        <v>3.684</v>
+      </c>
+      <c r="E10" s="1">
         <v>-50.2</v>
       </c>
-      <c r="F10" s="10">
-        <v>-0.007619</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="6" t="s">
+      <c r="F10" s="4">
+        <v>-0.006629</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="1">
         <v>-75</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="2">
         <v>2.5</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="3">
         <v>2.465</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="1">
         <v>-75</v>
       </c>
-      <c r="F11" s="10">
-        <v>-0.003455</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="6" t="s">
+      <c r="F11" s="4">
+        <v>-0.003459</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="1">
         <v>-100</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="2">
         <v>1.25</v>
       </c>
-      <c r="D12" s="9">
-        <v>1.224</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="D12" s="3">
+        <v>1.233</v>
+      </c>
+      <c r="E12" s="1">
         <v>-100</v>
       </c>
-      <c r="F12" s="10">
-        <v>-0.002621</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="6" t="s">
+      <c r="F12" s="4">
+        <v>-0.001706</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="1">
         <v>-125</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="2">
         <v>0</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="3">
         <v>0</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="1">
         <v>-125.2</v>
       </c>
-      <c r="F13" s="10">
+      <c r="F13" s="4">
+        <v>3E-06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="1">
+        <v>-165.7</v>
+      </c>
+      <c r="C14" s="2">
         <v>0</v>
       </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="7">
-        <v>-165.5</v>
-      </c>
-      <c r="C14" s="8">
+      <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="D14" s="9">
+      <c r="E14" s="1">
+        <v>-165.7</v>
+      </c>
+      <c r="F14" s="4">
         <v>0</v>
       </c>
-      <c r="E14" s="7">
-        <v>-165.5</v>
-      </c>
-      <c r="F14" s="10">
-        <v>0</v>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1">
+        <v>-43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="1">
+        <v>99.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="1">
+        <v>106.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="1">
+        <v>206.2</v>
       </c>
     </row>
   </sheetData>
